--- a/dentai-web/selenium-tests/reports/02_symptom_checker_report.xlsx
+++ b/dentai-web/selenium-tests/reports/02_symptom_checker_report.xlsx
@@ -443,7 +443,7 @@
         <v>Execution Timestamp</v>
       </c>
       <c r="B5" t="str">
-        <v>6/8/2026, 9:41:17 am</v>
+        <v>6/8/2026, 9:57:19 am</v>
       </c>
       <c r="C5" t="str">
         <v>Local Execution Time</v>
@@ -498,7 +498,7 @@
         <v>Total Suite Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>1.52 seconds</v>
+        <v>1.37 seconds</v>
       </c>
       <c r="C10" t="str">
         <v>Cumulative test runtime</v>
@@ -633,16 +633,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D2" t="str">
-        <v>WEB-SEL-051: Interactive Dental Chart Tooth #18 Selection</v>
+        <v>WEB-SEL-051: Interactive Dental Chart - Tooth #18 Upper Left Selection</v>
       </c>
       <c r="E2" t="str">
         <v>PASS</v>
       </c>
       <c r="F2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.369Z</v>
       </c>
       <c r="H2" t="str">
         <v>N/A</v>
@@ -659,16 +659,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D3" t="str">
-        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Trigger</v>
+        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Alert Trigger</v>
       </c>
       <c r="E3" t="str">
         <v>PASS</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H3" t="str">
         <v>N/A</v>
@@ -685,16 +685,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D4" t="str">
-        <v>WEB-SEL-053: Grumbling Sensitivity Hot/Cold Toggle State</v>
+        <v>WEB-SEL-053: Hot/Cold Temperature Sensitivity Toggle State</v>
       </c>
       <c r="E4" t="str">
         <v>PASS</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H4" t="str">
         <v>N/A</v>
@@ -711,16 +711,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D5" t="str">
-        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Check</v>
+        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Checklist</v>
       </c>
       <c r="E5" t="str">
         <v>PASS</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H5" t="str">
         <v>N/A</v>
@@ -737,16 +737,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D6" t="str">
-        <v>WEB-SEL-055: Jaw Clicking Joint Sound Questionnaire</v>
+        <v>WEB-SEL-055: Jaw Clicking Joint Sound Symptom Survey</v>
       </c>
       <c r="E6" t="str">
         <v>PASS</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H6" t="str">
         <v>N/A</v>
@@ -769,10 +769,10 @@
         <v>PASS</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H7" t="str">
         <v>N/A</v>
@@ -789,16 +789,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D8" t="str">
-        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge</v>
+        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge Render</v>
       </c>
       <c r="E8" t="str">
         <v>PASS</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H8" t="str">
         <v>N/A</v>
@@ -815,16 +815,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D9" t="str">
-        <v>WEB-SEL-058: High Priority Emergency Triage Banner Display</v>
+        <v>WEB-SEL-058: High Priority Emergency Triage Red Banner Display</v>
       </c>
       <c r="E9" t="str">
         <v>PASS</v>
       </c>
       <c r="F9">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H9" t="str">
         <v>N/A</v>
@@ -841,16 +841,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D10" t="str">
-        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Render</v>
+        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Summary View</v>
       </c>
       <c r="E10" t="str">
         <v>PASS</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H10" t="str">
         <v>N/A</v>
@@ -867,16 +867,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D11" t="str">
-        <v>WEB-SEL-060: Download Triage Report as PDF Document</v>
+        <v>WEB-SEL-060: Download Triage Report as PDF Document Stream</v>
       </c>
       <c r="E11" t="str">
         <v>PASS</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H11" t="str">
         <v>N/A</v>
@@ -893,16 +893,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D12" t="str">
-        <v>WEB-SEL-061: Share Symptom Summary via Direct Link</v>
+        <v>WEB-SEL-061: Share Symptom Summary via Temporary Direct Link</v>
       </c>
       <c r="E12" t="str">
         <v>PASS</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H12" t="str">
         <v>N/A</v>
@@ -925,10 +925,10 @@
         <v>PASS</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H13" t="str">
         <v>N/A</v>
@@ -945,16 +945,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D14" t="str">
-        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button</v>
+        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button Action</v>
       </c>
       <c r="E14" t="str">
         <v>PASS</v>
       </c>
       <c r="F14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H14" t="str">
         <v>N/A</v>
@@ -971,16 +971,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D15" t="str">
-        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search</v>
+        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search Input</v>
       </c>
       <c r="E15" t="str">
         <v>PASS</v>
       </c>
       <c r="F15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H15" t="str">
         <v>N/A</v>
@@ -997,16 +997,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D16" t="str">
-        <v>WEB-SEL-065: Filter Past Diagnoses by Severity Level</v>
+        <v>WEB-SEL-065: Filter Past Diagnoses by High/Medium Severity Level</v>
       </c>
       <c r="E16" t="str">
         <v>PASS</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G16" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H16" t="str">
         <v>N/A</v>
@@ -1023,16 +1023,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D17" t="str">
-        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR</v>
+        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR Payload</v>
       </c>
       <c r="E17" t="str">
         <v>PASS</v>
       </c>
       <c r="F17">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G17" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H17" t="str">
         <v>N/A</v>
@@ -1058,7 +1058,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H18" t="str">
         <v>N/A</v>
@@ -1081,10 +1081,10 @@
         <v>PASS</v>
       </c>
       <c r="F19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G19" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H19" t="str">
         <v>N/A</v>
@@ -1107,10 +1107,10 @@
         <v>PASS</v>
       </c>
       <c r="F20">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G20" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H20" t="str">
         <v>N/A</v>
@@ -1127,16 +1127,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D21" t="str">
-        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test</v>
+        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test Range</v>
       </c>
       <c r="E21" t="str">
         <v>PASS</v>
       </c>
       <c r="F21">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G21" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H21" t="str">
         <v>N/A</v>
@@ -1153,16 +1153,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D22" t="str">
-        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Flow</v>
+        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Survey Flow</v>
       </c>
       <c r="E22" t="str">
         <v>PASS</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G22" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H22" t="str">
         <v>N/A</v>
@@ -1179,16 +1179,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D23" t="str">
-        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Flow</v>
+        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Screener</v>
       </c>
       <c r="E23" t="str">
         <v>PASS</v>
       </c>
       <c r="F23">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G23" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H23" t="str">
         <v>N/A</v>
@@ -1205,16 +1205,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D24" t="str">
-        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping</v>
+        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping Click</v>
       </c>
       <c r="E24" t="str">
         <v>PASS</v>
       </c>
       <c r="F24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G24" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H24" t="str">
         <v>N/A</v>
@@ -1237,10 +1237,10 @@
         <v>PASS</v>
       </c>
       <c r="F25">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H25" t="str">
         <v>N/A</v>
@@ -1257,16 +1257,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D26" t="str">
-        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1-3)</v>
+        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1 to 3)</v>
       </c>
       <c r="E26" t="str">
         <v>PASS</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G26" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H26" t="str">
         <v>N/A</v>
@@ -1289,10 +1289,10 @@
         <v>PASS</v>
       </c>
       <c r="F27">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G27" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H27" t="str">
         <v>N/A</v>
@@ -1309,16 +1309,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D28" t="str">
-        <v>WEB-SEL-077: Dentural Soreness Point Location Click</v>
+        <v>WEB-SEL-077: Dentural Soreness Point Location Click Target</v>
       </c>
       <c r="E28" t="str">
         <v>PASS</v>
       </c>
       <c r="F28">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G28" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H28" t="str">
         <v>N/A</v>
@@ -1335,16 +1335,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D29" t="str">
-        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey</v>
+        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey Check</v>
       </c>
       <c r="E29" t="str">
         <v>PASS</v>
       </c>
       <c r="F29">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G29" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H29" t="str">
         <v>N/A</v>
@@ -1367,10 +1367,10 @@
         <v>PASS</v>
       </c>
       <c r="F30">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G30" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H30" t="str">
         <v>N/A</v>
@@ -1393,10 +1393,10 @@
         <v>PASS</v>
       </c>
       <c r="F31">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G31" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H31" t="str">
         <v>N/A</v>
@@ -1419,10 +1419,10 @@
         <v>PASS</v>
       </c>
       <c r="F32">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G32" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H32" t="str">
         <v>N/A</v>
@@ -1445,10 +1445,10 @@
         <v>PASS</v>
       </c>
       <c r="F33">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G33" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H33" t="str">
         <v>N/A</v>
@@ -1471,10 +1471,10 @@
         <v>PASS</v>
       </c>
       <c r="F34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G34" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H34" t="str">
         <v>N/A</v>
@@ -1497,10 +1497,10 @@
         <v>PASS</v>
       </c>
       <c r="F35">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G35" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H35" t="str">
         <v>N/A</v>
@@ -1523,10 +1523,10 @@
         <v>PASS</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G36" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H36" t="str">
         <v>N/A</v>
@@ -1549,10 +1549,10 @@
         <v>PASS</v>
       </c>
       <c r="F37">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G37" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H37" t="str">
         <v>N/A</v>
@@ -1575,10 +1575,10 @@
         <v>PASS</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G38" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H38" t="str">
         <v>N/A</v>
@@ -1601,10 +1601,10 @@
         <v>PASS</v>
       </c>
       <c r="F39">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G39" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H39" t="str">
         <v>N/A</v>
@@ -1627,10 +1627,10 @@
         <v>PASS</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G40" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H40" t="str">
         <v>N/A</v>
@@ -1647,16 +1647,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D41" t="str">
-        <v>WEB-SEL-090: Salivary Gland Blockage Assessment</v>
+        <v>WEB-SEL-090: Salivary Gland Blockage Assessment Flow</v>
       </c>
       <c r="E41" t="str">
         <v>PASS</v>
       </c>
       <c r="F41">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G41" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H41" t="str">
         <v>N/A</v>
@@ -1673,16 +1673,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D42" t="str">
-        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment</v>
+        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment Survey</v>
       </c>
       <c r="E42" t="str">
         <v>PASS</v>
       </c>
       <c r="F42">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G42" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H42" t="str">
         <v>N/A</v>
@@ -1699,16 +1699,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D43" t="str">
-        <v>WEB-SEL-092: Tongue Lesion Color Selector</v>
+        <v>WEB-SEL-092: Tongue Lesion Color Selector Option</v>
       </c>
       <c r="E43" t="str">
         <v>PASS</v>
       </c>
       <c r="F43">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G43" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H43" t="str">
         <v>N/A</v>
@@ -1731,10 +1731,10 @@
         <v>PASS</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G44" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H44" t="str">
         <v>N/A</v>
@@ -1757,10 +1757,10 @@
         <v>PASS</v>
       </c>
       <c r="F45">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G45" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H45" t="str">
         <v>N/A</v>
@@ -1777,16 +1777,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D46" t="str">
-        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert</v>
+        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert Trigger</v>
       </c>
       <c r="E46" t="str">
         <v>PASS</v>
       </c>
       <c r="F46">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G46" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H46" t="str">
         <v>N/A</v>
@@ -1809,10 +1809,10 @@
         <v>PASS</v>
       </c>
       <c r="F47">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G47" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H47" t="str">
         <v>N/A</v>
@@ -1835,10 +1835,10 @@
         <v>PASS</v>
       </c>
       <c r="F48">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G48" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H48" t="str">
         <v>N/A</v>
@@ -1855,16 +1855,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D49" t="str">
-        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3</v>
+        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3 Wizard</v>
       </c>
       <c r="E49" t="str">
         <v>PASS</v>
       </c>
       <c r="F49">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G49" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H49" t="str">
         <v>N/A</v>
@@ -1881,16 +1881,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D50" t="str">
-        <v>WEB-SEL-099: Back Button State Preservation in Wizard</v>
+        <v>WEB-SEL-099: Back Button State Preservation in Symptom Wizard</v>
       </c>
       <c r="E50" t="str">
         <v>PASS</v>
       </c>
       <c r="F50">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="G50" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H50" t="str">
         <v>N/A</v>
@@ -1907,16 +1907,16 @@
         <v>Selenium Web E2E Suite - 02_symptom_checker.test.js</v>
       </c>
       <c r="D51" t="str">
-        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card</v>
+        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card View</v>
       </c>
       <c r="E51" t="str">
         <v>PASS</v>
       </c>
       <c r="F51">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G51" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="H51" t="str">
         <v>N/A</v>
@@ -1973,16 +1973,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C2" t="str">
-        <v>WEB-SEL-051: Interactive Dental Chart Tooth #18 Selection</v>
+        <v>WEB-SEL-051: Interactive Dental Chart - Tooth #18 Upper Left Selection</v>
       </c>
       <c r="D2" t="str">
         <v>PASS</v>
       </c>
       <c r="E2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.369Z</v>
       </c>
       <c r="G2" t="str">
         <v>N/A</v>
@@ -1996,16 +1996,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C3" t="str">
-        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Trigger</v>
+        <v>WEB-SEL-052: Pain Severity Slider Value 8 Threshold Alert Trigger</v>
       </c>
       <c r="D3" t="str">
         <v>PASS</v>
       </c>
       <c r="E3">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G3" t="str">
         <v>N/A</v>
@@ -2019,16 +2019,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C4" t="str">
-        <v>WEB-SEL-053: Grumbling Sensitivity Hot/Cold Toggle State</v>
+        <v>WEB-SEL-053: Hot/Cold Temperature Sensitivity Toggle State</v>
       </c>
       <c r="D4" t="str">
         <v>PASS</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G4" t="str">
         <v>N/A</v>
@@ -2042,16 +2042,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C5" t="str">
-        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Check</v>
+        <v>WEB-SEL-054: Bleeding Gums Frequency Selection Checklist</v>
       </c>
       <c r="D5" t="str">
         <v>PASS</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G5" t="str">
         <v>N/A</v>
@@ -2065,16 +2065,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C6" t="str">
-        <v>WEB-SEL-055: Jaw Clicking Joint Sound Questionnaire</v>
+        <v>WEB-SEL-055: Jaw Clicking Joint Sound Symptom Survey</v>
       </c>
       <c r="D6" t="str">
         <v>PASS</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G6" t="str">
         <v>N/A</v>
@@ -2094,10 +2094,10 @@
         <v>PASS</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G7" t="str">
         <v>N/A</v>
@@ -2111,16 +2111,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C8" t="str">
-        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge</v>
+        <v>WEB-SEL-057: Dynamic Severity Score Calculation Badge Render</v>
       </c>
       <c r="D8" t="str">
         <v>PASS</v>
       </c>
       <c r="E8">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G8" t="str">
         <v>N/A</v>
@@ -2134,16 +2134,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C9" t="str">
-        <v>WEB-SEL-058: High Priority Emergency Triage Banner Display</v>
+        <v>WEB-SEL-058: High Priority Emergency Triage Red Banner Display</v>
       </c>
       <c r="D9" t="str">
         <v>PASS</v>
       </c>
       <c r="E9">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G9" t="str">
         <v>N/A</v>
@@ -2157,16 +2157,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C10" t="str">
-        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Render</v>
+        <v>WEB-SEL-059: Differential Diagnosis Matrix Table Summary View</v>
       </c>
       <c r="D10" t="str">
         <v>PASS</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G10" t="str">
         <v>N/A</v>
@@ -2180,16 +2180,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C11" t="str">
-        <v>WEB-SEL-060: Download Triage Report as PDF Document</v>
+        <v>WEB-SEL-060: Download Triage Report as PDF Document Stream</v>
       </c>
       <c r="D11" t="str">
         <v>PASS</v>
       </c>
       <c r="E11">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G11" t="str">
         <v>N/A</v>
@@ -2203,16 +2203,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C12" t="str">
-        <v>WEB-SEL-061: Share Symptom Summary via Direct Link</v>
+        <v>WEB-SEL-061: Share Symptom Summary via Temporary Direct Link</v>
       </c>
       <c r="D12" t="str">
         <v>PASS</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G12" t="str">
         <v>N/A</v>
@@ -2232,10 +2232,10 @@
         <v>PASS</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G13" t="str">
         <v>N/A</v>
@@ -2249,16 +2249,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C14" t="str">
-        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button</v>
+        <v>WEB-SEL-063: Clear All Symptom Selection Reset Button Action</v>
       </c>
       <c r="D14" t="str">
         <v>PASS</v>
       </c>
       <c r="E14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G14" t="str">
         <v>N/A</v>
@@ -2272,16 +2272,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C15" t="str">
-        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search</v>
+        <v>WEB-SEL-064: Symptom History List Navigation &amp; Search Input</v>
       </c>
       <c r="D15" t="str">
         <v>PASS</v>
       </c>
       <c r="E15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G15" t="str">
         <v>N/A</v>
@@ -2295,16 +2295,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C16" t="str">
-        <v>WEB-SEL-065: Filter Past Diagnoses by Severity Level</v>
+        <v>WEB-SEL-065: Filter Past Diagnoses by High/Medium Severity Level</v>
       </c>
       <c r="D16" t="str">
         <v>PASS</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G16" t="str">
         <v>N/A</v>
@@ -2318,16 +2318,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C17" t="str">
-        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR</v>
+        <v>WEB-SEL-066: Export Diagnostic Record to Medical EHR Payload</v>
       </c>
       <c r="D17" t="str">
         <v>PASS</v>
       </c>
       <c r="E17">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G17" t="str">
         <v>N/A</v>
@@ -2350,7 +2350,7 @@
         <v>19</v>
       </c>
       <c r="F18" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G18" t="str">
         <v>N/A</v>
@@ -2370,10 +2370,10 @@
         <v>PASS</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F19" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G19" t="str">
         <v>N/A</v>
@@ -2393,10 +2393,10 @@
         <v>PASS</v>
       </c>
       <c r="E20">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F20" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G20" t="str">
         <v>N/A</v>
@@ -2410,16 +2410,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C21" t="str">
-        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test</v>
+        <v>WEB-SEL-070: Enamel Erosion Sensitivity Slider Test Range</v>
       </c>
       <c r="D21" t="str">
         <v>PASS</v>
       </c>
       <c r="E21">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F21" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G21" t="str">
         <v>N/A</v>
@@ -2433,16 +2433,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C22" t="str">
-        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Flow</v>
+        <v>WEB-SEL-071: Dry Mouth Symptoms Assessment Survey Flow</v>
       </c>
       <c r="D22" t="str">
         <v>PASS</v>
       </c>
       <c r="E22">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F22" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G22" t="str">
         <v>N/A</v>
@@ -2456,16 +2456,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C23" t="str">
-        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Flow</v>
+        <v>WEB-SEL-072: Bad Breath (Halitosis) Diagnostics Screener</v>
       </c>
       <c r="D23" t="str">
         <v>PASS</v>
       </c>
       <c r="E23">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F23" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G23" t="str">
         <v>N/A</v>
@@ -2479,16 +2479,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C24" t="str">
-        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping</v>
+        <v>WEB-SEL-073: Canker Sore / Ulcer Location Mapping Click</v>
       </c>
       <c r="D24" t="str">
         <v>PASS</v>
       </c>
       <c r="E24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F24" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G24" t="str">
         <v>N/A</v>
@@ -2508,10 +2508,10 @@
         <v>PASS</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F25" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G25" t="str">
         <v>N/A</v>
@@ -2525,16 +2525,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C26" t="str">
-        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1-3)</v>
+        <v>WEB-SEL-075: Loose Tooth Mobility Rating (Grade 1 to 3)</v>
       </c>
       <c r="D26" t="str">
         <v>PASS</v>
       </c>
       <c r="E26">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F26" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G26" t="str">
         <v>N/A</v>
@@ -2554,10 +2554,10 @@
         <v>PASS</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F27" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G27" t="str">
         <v>N/A</v>
@@ -2571,16 +2571,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C28" t="str">
-        <v>WEB-SEL-077: Dentural Soreness Point Location Click</v>
+        <v>WEB-SEL-077: Dentural Soreness Point Location Click Target</v>
       </c>
       <c r="D28" t="str">
         <v>PASS</v>
       </c>
       <c r="E28">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F28" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G28" t="str">
         <v>N/A</v>
@@ -2594,16 +2594,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C29" t="str">
-        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey</v>
+        <v>WEB-SEL-078: Orthodontic Wire Irritation Survey Check</v>
       </c>
       <c r="D29" t="str">
         <v>PASS</v>
       </c>
       <c r="E29">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F29" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G29" t="str">
         <v>N/A</v>
@@ -2623,10 +2623,10 @@
         <v>PASS</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F30" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G30" t="str">
         <v>N/A</v>
@@ -2646,10 +2646,10 @@
         <v>PASS</v>
       </c>
       <c r="E31">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F31" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G31" t="str">
         <v>N/A</v>
@@ -2669,10 +2669,10 @@
         <v>PASS</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F32" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G32" t="str">
         <v>N/A</v>
@@ -2692,10 +2692,10 @@
         <v>PASS</v>
       </c>
       <c r="E33">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F33" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G33" t="str">
         <v>N/A</v>
@@ -2715,10 +2715,10 @@
         <v>PASS</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F34" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G34" t="str">
         <v>N/A</v>
@@ -2738,10 +2738,10 @@
         <v>PASS</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F35" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G35" t="str">
         <v>N/A</v>
@@ -2761,10 +2761,10 @@
         <v>PASS</v>
       </c>
       <c r="E36">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F36" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G36" t="str">
         <v>N/A</v>
@@ -2784,10 +2784,10 @@
         <v>PASS</v>
       </c>
       <c r="E37">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F37" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G37" t="str">
         <v>N/A</v>
@@ -2807,10 +2807,10 @@
         <v>PASS</v>
       </c>
       <c r="E38">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F38" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G38" t="str">
         <v>N/A</v>
@@ -2830,10 +2830,10 @@
         <v>PASS</v>
       </c>
       <c r="E39">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F39" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G39" t="str">
         <v>N/A</v>
@@ -2853,10 +2853,10 @@
         <v>PASS</v>
       </c>
       <c r="E40">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F40" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G40" t="str">
         <v>N/A</v>
@@ -2870,16 +2870,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C41" t="str">
-        <v>WEB-SEL-090: Salivary Gland Blockage Assessment</v>
+        <v>WEB-SEL-090: Salivary Gland Blockage Assessment Flow</v>
       </c>
       <c r="D41" t="str">
         <v>PASS</v>
       </c>
       <c r="E41">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F41" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G41" t="str">
         <v>N/A</v>
@@ -2893,16 +2893,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C42" t="str">
-        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment</v>
+        <v>WEB-SEL-091: Mouth Breathing / Airway Assessment Survey</v>
       </c>
       <c r="D42" t="str">
         <v>PASS</v>
       </c>
       <c r="E42">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F42" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G42" t="str">
         <v>N/A</v>
@@ -2916,16 +2916,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C43" t="str">
-        <v>WEB-SEL-092: Tongue Lesion Color Selector</v>
+        <v>WEB-SEL-092: Tongue Lesion Color Selector Option</v>
       </c>
       <c r="D43" t="str">
         <v>PASS</v>
       </c>
       <c r="E43">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F43" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G43" t="str">
         <v>N/A</v>
@@ -2945,10 +2945,10 @@
         <v>PASS</v>
       </c>
       <c r="E44">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F44" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G44" t="str">
         <v>N/A</v>
@@ -2968,10 +2968,10 @@
         <v>PASS</v>
       </c>
       <c r="E45">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F45" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G45" t="str">
         <v>N/A</v>
@@ -2985,16 +2985,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C46" t="str">
-        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert</v>
+        <v>WEB-SEL-095: Difficulty Swallowing (Dysphagia) Alert Trigger</v>
       </c>
       <c r="D46" t="str">
         <v>PASS</v>
       </c>
       <c r="E46">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F46" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G46" t="str">
         <v>N/A</v>
@@ -3014,10 +3014,10 @@
         <v>PASS</v>
       </c>
       <c r="E47">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F47" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G47" t="str">
         <v>N/A</v>
@@ -3037,10 +3037,10 @@
         <v>PASS</v>
       </c>
       <c r="E48">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F48" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G48" t="str">
         <v>N/A</v>
@@ -3054,16 +3054,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C49" t="str">
-        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3</v>
+        <v>WEB-SEL-098: Auto-save Progress Indicator on Step 3 Wizard</v>
       </c>
       <c r="D49" t="str">
         <v>PASS</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F49" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G49" t="str">
         <v>N/A</v>
@@ -3077,16 +3077,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C50" t="str">
-        <v>WEB-SEL-099: Back Button State Preservation in Wizard</v>
+        <v>WEB-SEL-099: Back Button State Preservation in Symptom Wizard</v>
       </c>
       <c r="D50" t="str">
         <v>PASS</v>
       </c>
       <c r="E50">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F50" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G50" t="str">
         <v>N/A</v>
@@ -3100,16 +3100,16 @@
         <v>E2E Functional</v>
       </c>
       <c r="C51" t="str">
-        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card</v>
+        <v>WEB-SEL-100: Final Triage Doctor Recommendation Card View</v>
       </c>
       <c r="D51" t="str">
         <v>PASS</v>
       </c>
       <c r="E51">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="F51" t="str">
-        <v>2026-08-06T04:11:17.927Z</v>
+        <v>2026-08-06T04:27:19.370Z</v>
       </c>
       <c r="G51" t="str">
         <v>N/A</v>
